--- a/output/아이콘관리_TC_마스터_테스트.xlsx
+++ b/output/아이콘관리_TC_마스터_테스트.xlsx
@@ -646,7 +646,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H5" s="2" t="n"/>
@@ -675,8 +675,8 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>[검색] 버튼을 클릭
-검색 결과 목록을 확인</t>
+          <t>1. [검색] 버튼을 클릭
+2. 검색 결과 목록을 확인</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H6" s="2" t="n"/>
@@ -715,8 +715,8 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>[검색] 버튼을 클릭
-검색 결과 목록을 확인</t>
+          <t>1. [검색] 버튼을 클릭
+2. 검색 결과 목록을 확인</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H7" s="2" t="n"/>
@@ -765,7 +765,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H8" s="2" t="n"/>
@@ -804,7 +804,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H9" s="2" t="n"/>
@@ -833,8 +833,8 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>'전체' 항목을 클릭
-유형 구분 필터의 선택 상태를 확인</t>
+          <t>1. '전체' 항목을 클릭
+2. 유형 구분 필터의 선택 상태를 확인</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H10" s="2" t="n"/>
@@ -873,9 +873,8 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>'전체'를 제외한 텍스트
-이미지 항목을 모두 선택
-'전체' 항목 선택 상태를 확인</t>
+          <t>1. '전체'를 제외한 텍스트 / 이미지 항목을 모두 선택
+2. '전체' 항목 선택 상태를 확인</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -885,7 +884,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H11" s="2" t="n"/>
@@ -924,7 +923,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H12" s="2" t="n"/>
@@ -953,8 +952,8 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>'전체' 항목을 클릭
-사용 여부 필터의 선택 상태를 확인</t>
+          <t>1. '전체' 항목을 클릭
+2. 사용 여부 필터의 선택 상태를 확인</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -964,7 +963,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H13" s="2" t="n"/>
@@ -993,9 +992,8 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>'전체'를 제외한 '사용'
-'사용 안 함' 항목을 모두 선택
-'전체' 항목 선택 상태를 확인</t>
+          <t>1. '전체'를 제외한 '사용' / '사용 안 함' 항목을 모두 선택
+2. '전체' 항목 선택 상태를 확인</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -1005,7 +1003,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H14" s="2" t="n"/>
@@ -1034,8 +1032,8 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>[검색] 버튼을 클릭
-검색 결과를 확인</t>
+          <t>1. [검색] 버튼을 클릭
+2. 검색 결과를 확인</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -1045,7 +1043,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H15" s="2" t="n"/>
@@ -1074,8 +1072,8 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>검색어 입력 필드에서 Enter 키를 입력
-검색 결과를 확인</t>
+          <t>1. 검색어 입력 필드에서 Enter 키를 입력
+2. 검색 결과를 확인</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -1085,7 +1083,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H16" s="2" t="n"/>
@@ -1114,8 +1112,8 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>[검색] 버튼을 클릭
-결과 영역을 확인</t>
+          <t>1. [검색] 버튼을 클릭
+2. 결과 영역을 확인</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -1125,7 +1123,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H17" s="2" t="n"/>
@@ -1154,8 +1152,8 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>[초기화] 버튼을 클릭
-검색 조건 영역의 상태를 확인</t>
+          <t>1. [초기화] 버튼을 클릭
+2. 검색 조건 영역의 상태를 확인</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -1165,7 +1163,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H18" s="2" t="n"/>
@@ -1194,8 +1192,8 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>[초기화] 버튼을 클릭
-결과 항목 선택 상태를 확인</t>
+          <t>1. [초기화] 버튼을 클릭
+2. 결과 항목 선택 상태를 확인</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -1205,7 +1203,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H19" s="2" t="n"/>
@@ -1234,8 +1232,8 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>[아이콘 등록] 버튼을 클릭
-브라우저 탭 상태를 확인</t>
+          <t>1. [아이콘 등록] 버튼을 클릭
+2. 브라우저 탭 상태를 확인</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -1245,7 +1243,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H20" s="2" t="n"/>
@@ -1274,8 +1272,8 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>[초기화] 버튼을 클릭
-결과 목록의 상태를 확인</t>
+          <t>1. [초기화] 버튼을 클릭
+2. 결과 목록의 상태를 확인</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -1285,7 +1283,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H21" s="2" t="n"/>
@@ -1314,8 +1312,8 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>[초기화] 버튼을 클릭
-검색 조건 영역의 상태를 확인</t>
+          <t>1. [초기화] 버튼을 클릭
+2. 검색 조건 영역의 상태를 확인</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -1325,7 +1323,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H22" s="2" t="n"/>
@@ -1549,8 +1547,8 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>결과 영역을 아래로 스크롤
-검색 조건 영역의 위치를 확인</t>
+          <t>1. 결과 영역을 아래로 스크롤
+2. 검색 조건 영역의 위치를 확인</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -1589,8 +1587,8 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>결과 리스트 영역을 좌우로 스크롤
-화면 밖의 열 노출 여부를 확인</t>
+          <t>1. 결과 리스트 영역을 좌우로 스크롤
+2. 화면 밖의 열 노출 여부를 확인</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -1824,8 +1822,8 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>아이콘 수정 후 저장
-결과 리스트에서 해당 항목의 수정일 컬럼을 확인</t>
+          <t>1. 아이콘 수정 후 저장
+2. 결과 리스트에서 해당 항목의 수정일 컬럼을 확인</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -1864,8 +1862,8 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>결과 목록에서 특정 항목의 '수정' 문구를 클릭
-브라우저 탭 상태를 확인</t>
+          <t>1. 결과 목록에서 특정 항목의 '수정' 문구를 클릭
+2. 브라우저 탭 상태를 확인</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
@@ -1904,8 +1902,8 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>결과 목록에서 특정 항목의 아이콘 번호를 클릭
-브라우저 탭 상태를 확인</t>
+          <t>1. 결과 목록에서 특정 항목의 아이콘 번호를 클릭
+2. 브라우저 탭 상태를 확인</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -1944,8 +1942,8 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>결과 영역을 아래로 스크롤
-결과 영역의 스크롤 동작을 확인</t>
+          <t>1. 결과 영역을 아래로 스크롤
+2. 결과 영역의 스크롤 동작을 확인</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
